--- a/assets/bill-template.xlsx
+++ b/assets/bill-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects And Work\attendance-portal\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A82496-F1E8-4551-A2CA-B0CC3E453564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F949BF2B-DFA9-4370-AFDA-5C071FD073C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>INDIRA GANDHI NATIONAL OPEN UNIVERSITY,</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Programme: __________________________</t>
+  </si>
+  <si>
+    <t>Date:_______________________________</t>
   </si>
 </sst>
 </file>
@@ -195,44 +198,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -493,515 +502,512 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G1" s="13"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G2" s="13"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="12" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4" t="s">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="9" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="9" t="s">
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+      <c r="A13" s="3">
         <v>1</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+      <c r="A14" s="3">
         <v>2</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+      <c r="A15" s="3">
         <v>3</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
     </row>
     <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+      <c r="A16" s="3">
         <v>4</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
         <v>5</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
         <v>6</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
         <v>7</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
         <v>8</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
         <v>9</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
         <v>10</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="4" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="9">
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="2">
         <f>SUM(J13:J24)</f>
         <v>0</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="2">
         <f>SUM(K13:K24)</f>
         <v>0</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="2">
         <f>SUM(L13:L24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="29" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+    </row>
+    <row r="29" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="32" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J31" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="2" t="s">
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="36" spans="1:12" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3" t="s">
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+    </row>
+    <row r="38" spans="1:14" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F38" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-    </row>
-    <row r="38" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+    </row>
+    <row r="40" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J44" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="F35:L35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="F36:L36"/>
-    <mergeCell ref="A38:L38"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="F32:L32"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:I11"/>
+  <mergeCells count="28">
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="F38:N38"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
@@ -1010,6 +1016,24 @@
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="G8:L8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="F36:L36"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="J31:N31"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
